--- a/tables/Table2_subsidy_type.xlsx
+++ b/tables/Table2_subsidy_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65B0B74-D9AC-BE45-A877-4457D9CE6D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D892722D-2600-CA45-9139-11BCF17EF59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="500" windowWidth="27340" windowHeight="21900" xr2:uid="{57AECC44-64E1-E746-BEE1-FAFADCE44C53}"/>
+    <workbookView xWindow="1560" yWindow="660" windowWidth="27340" windowHeight="18460" xr2:uid="{57AECC44-64E1-E746-BEE1-FAFADCE44C53}"/>
   </bookViews>
   <sheets>
     <sheet name="Formatted" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="58">
   <si>
     <t>Buy out vessels and permits for fishermen opting to exit fishery</t>
   </si>
@@ -209,6 +209,15 @@
   </si>
   <si>
     <t>Marketing, processing and storage, infrastructure and support</t>
+  </si>
+  <si>
+    <t>Sustainably relax fishing regulations</t>
+  </si>
+  <si>
+    <t>Subsidized lending for infrastructure and capital cost support</t>
+  </si>
+  <si>
+    <t>Vessel buybacks; Permit and license retirement</t>
   </si>
 </sst>
 </file>
@@ -279,17 +288,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,10 +642,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C1" s="1"/>
@@ -651,7 +659,7 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="1"/>
@@ -659,66 +667,66 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
+      <c r="B7" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -726,89 +734,89 @@
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="2"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="2"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -816,113 +824,113 @@
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="4" t="s">
+      <c r="A37" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
+      <c r="A40" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -935,10 +943,9 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="58.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="58.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -956,352 +963,352 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>16</v>
       </c>
     </row>
